--- a/Result/profitability/3162.xlsx
+++ b/Result/profitability/3162.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.09</v>
       </c>
       <c r="M2" t="n">
-        <v>0.38375</v>
+        <v>0.3575</v>
       </c>
       <c r="N2" t="n">
-        <v>12.8925</v>
+        <v>12.76875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.33</v>
       </c>
       <c r="M3" t="n">
-        <v>0.395</v>
+        <v>0.25</v>
       </c>
       <c r="N3" t="n">
-        <v>13.5125</v>
+        <v>13.18375</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3325</v>
+        <v>0.27375</v>
       </c>
       <c r="N4" t="n">
-        <v>14.86375</v>
+        <v>14.61125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3175</v>
+        <v>0.25625</v>
       </c>
       <c r="N5" t="n">
-        <v>14.995</v>
+        <v>14.60875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24</v>
+        <v>0.215</v>
       </c>
       <c r="N6" t="n">
-        <v>14.20375</v>
+        <v>14.295</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>0.20875</v>
+        <v>0.155</v>
       </c>
       <c r="N7" t="n">
-        <v>14.93</v>
+        <v>14.9125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1825</v>
+        <v>0.18375</v>
       </c>
       <c r="N8" t="n">
-        <v>16.045</v>
+        <v>16.175</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3162</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2387</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2113</v>
+      </c>
+      <c r="E75" t="n">
+        <v>273</v>
+      </c>
+      <c r="F75" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="G75" t="n">
+        <v>44</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.84%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.3375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.009999999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09990393852065305</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9423076923076923</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2125171939477304</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
